--- a/stick-world/config/excel/扩张数据.xlsx
+++ b/stick-world/config/excel/扩张数据.xlsx
@@ -570,7 +570,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>炎炉山脉</t>
+          <t>火山山脉</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>赤砂荒原</t>
+          <t>沙漠荒原</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>碧波群岛</t>
+          <t>海洋群岛</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>苍翠密林</t>
+          <t>森林</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -818,6 +818,11 @@
           <t>#output_dir: expansion</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t># 命名与映射为 AI 提案/待定（国家层 P5 接入前不定稿；命名口径见 docs/设计/命名与数值口径.md）</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -923,7 +928,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>炎炉部落</t>
+          <t>火山部落</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -987,7 +992,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>赤砂汗国</t>
+          <t>沙漠汗国</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1019,7 +1024,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>碧波联邦</t>
+          <t>海洋联邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1051,7 +1056,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>苍翠猎团</t>
+          <t>森林猎团</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
